--- a/aq_files/0103.xlsx
+++ b/aq_files/0103.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Compare means of 3+ groups. Which test?</t>
-  </si>
-  <si>
-    <t>What does ANOVA stand for?</t>
-  </si>
-  <si>
-    <t>What is null hypothesis?</t>
-  </si>
-  <si>
-    <t>What is alternative hypothesis?</t>
-  </si>
-  <si>
-    <t>What is F-statistic?</t>
-  </si>
-  <si>
-    <t>What is between-group variance?</t>
-  </si>
-  <si>
-    <t>What is within-group variance?</t>
-  </si>
-  <si>
-    <t>Why use ANOVA instead of multiple t-tests?</t>
-  </si>
-  <si>
-    <t>What does large F indicate?</t>
-  </si>
-  <si>
-    <t>What is significance?</t>
-  </si>
-  <si>
-    <t>What is post-hoc test?</t>
-  </si>
-  <si>
-    <t>What is assumption?</t>
-  </si>
-  <si>
-    <t>What is homogeneity of variance?</t>
-  </si>
-  <si>
-    <t>What is independence?</t>
-  </si>
-  <si>
-    <t>What happens if p &lt; 0.05?</t>
-  </si>
-  <si>
-    <t>Example: 3 teaching methods. Which test?</t>
-  </si>
-  <si>
-    <t>What is factor?</t>
-  </si>
-  <si>
-    <t>What is level?</t>
-  </si>
-  <si>
-    <t>What is variance ratio?</t>
-  </si>
-  <si>
-    <t>Why ANOVA is important?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1033 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order_ID,Order_Date,Year,Quarter,Month,Week,Region,State,City,Product_Category,Sub_Category,Product_Name,Sales,Quantity,Profit,Discount,Shipping_Cost,Customer_Segment,Sales_Rep,Customer_Age,Order_Processing_Days,Delivery_Days,Return_Flag</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7001,2024-01-01,2024,Q1,January,1,North,Illinois,Chicago,Electronics,Computers,MacBook Pro,2499.99,2,749.98,0.10,25.00,Corporate,John Smith,45,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7002,2024-01-01,2024,Q1,January,1,North,Illinois,Chicago,Electronics,Accessories,Magic Mouse,89.99,5,26.99,0.05,8.50,Corporate,John Smith,45,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7003,2024-01-02,2024,Q1,January,1,South,Texas,Houston,Clothing,Mens,Designer Jeans,99.99,8,29.99,0.00,12.00,Consumer,Sarah Lee,28,3,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7004,2024-01-02,2024,Q1,January,1,South,Texas,Austin,Electronics,Monitors,4K Monitor,449.99,3,134.99,0.15,18.00,Consumer,Sarah Lee,32,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7005,2024-01-03,2024,Q1,January,1,East,New York,New York,Furniture,Chairs,Executive Chair,449.99,2,134.99,0.05,22.00,Corporate,Michael Brown,52,3,5,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7006,2024-01-03,2024,Q1,January,1,East,New York,Buffalo,Electronics,Keyboards,Mechanical Keyboard,129.99,4,38.99,0.10,10.00,Consumer,Michael Brown,26,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7007,2024-01-04,2024,Q1,January,1,West,California,Los Angeles,Clothing,Womens,Leather Jacket,199.99,3,59.99,0.20,15.00,Home Office,Emily Davis,34,2,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7008,2024-01-04,2024,Q1,January,1,West,California,San Francisco,Electronics,Tablets,iPad Air,599.99,2,179.99,0.05,20.00,Corporate,Emily Davis,41,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7009,2024-01-05,2024,Q1,January,1,North,Illinois,Chicago,Furniture,Lighting,Floor Lamp,89.99,5,26.99,0.00,12.00,Consumer,John Smith,38,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7010,2024-01-05,2024,Q1,January,1,North,Michigan,Detroit,Clothing,Mens,Running Shoes,79.99,6,23.99,0.10,10.00,Consumer,John Smith,29,2,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7011,2024-01-08,2024,Q1,January,2,South,Texas,Dallas,Electronics,Computers,Gaming Laptop,1599.99,1,479.99,0.15,25.00,Corporate,Sarah Lee,35,3,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7012,2024-01-08,2024,Q1,January,2,East,Pennsylvania,Philadelphia,Electronics,Audio,Headphones,199.99,3,59.99,0.05,12.00,Consumer,Michael Brown,27,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7013,2024-01-09,2024,Q1,January,2,West,California,San Diego,Clothing,Womens,Wool Coat,249.99,2,74.99,0.20,15.00,Home Office,Emily Davis,39,2,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7014,2024-01-09,2024,Q1,January,2,North,Ohio,Columbus,Furniture,Storage,Bookshelf,189.99,2,56.99,0.10,18.00,Corporate,John Smith,47,3,5,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7015,2024-01-10,2024,Q1,January,2,South,Florida,Miami,Electronics,Phones,Smartphone,799.99,3,239.99,0.05,12.00,Consumer,Sarah Lee,31,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7016,2024-01-10,2024,Q1,January,2,East,New York,New York,Clothing,Mens,Dress Shirt,69.99,8,20.99,0.00,10.00,Corporate,Michael Brown,44,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7017,2024-01-11,2024,Q1,January,2,West,Oregon,Portland,Electronics,Storage,External SSD,129.99,3,38.99,0.10,8.50,Consumer,Emily Davis,33,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7018,2024-01-11,2024,Q1,January,2,North,Illinois,Chicago,Clothing,Womens,Hoodie,59.99,10,17.99,0.05,12.00,Consumer,John Smith,25,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7019,2024-01-12,2024,Q1,January,2,South,Texas,Austin,Furniture,Desks,Gaming Desk,399.99,1,119.99,0.15,25.00,Corporate,Sarah Lee,42,3,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7020,2024-01-12,2024,Q1,January,2,East,Massachusetts,Boston,Electronics,Accessories,Webcam,89.99,4,26.99,0.10,8.50,Home Office,Michael Brown,36,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7021,2024-02-01,2024,Q1,February,5,West,Washington,Seattle,Electronics,Docks,Docking Station,149.99,3,44.99,0.00,10.00,Consumer,Emily Davis,40,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7022,2024-02-01,2024,Q1,February,5,North,Minnesota,Minneapolis,Clothing,Mens,Winter Parka,199.99,3,59.99,0.05,15.00,Consumer,John Smith,48,2,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7023,2024-02-02,2024,Q1,February,5,South,Florida,Orlando,Furniture,Desks,Office Desk,499.99,2,149.99,0.10,22.00,Corporate,Sarah Lee,53,3,5,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7024,2024-02-02,2024,Q1,February,5,East,New Jersey,Newark,Electronics,Cables,USB-C Hub,49.99,8,14.99,0.00,8.50,Consumer,Michael Brown,24,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7025,2024-02-03,2024,Q1,February,5,West,California,Los Angeles,Clothing,Mens,Casual Blazer,159.99,4,47.99,0.15,12.00,Home Office,Emily Davis,37,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7026,2024-02-03,2024,Q1,February,5,North,Indiana,Indianapolis,Electronics,Accessories,Gaming Mouse,69.99,8,20.99,0.10,8.50,Consumer,John Smith,22,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7027,2024-02-04,2024,Q1,February,5,South,Georgia,Atlanta,Electronics,Printers,Laser Printer,249.99,2,74.99,0.05,18.00,Corporate,Sarah Lee,49,2,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7028,2024-02-04,2024,Q1,February,5,East,Virginia,Richmond,Furniture,Chairs,Lounge Chair,329.99,2,98.99,0.20,22.00,Consumer,Michael Brown,56,3,5,TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7029,2024-02-05,2024,Q1,February,6,West,Arizona,Phoenix,Electronics,Batteries,Power Bank,59.99,12,17.99,0.00,8.50,Consumer,Emily Davis,30,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7030,2024-02-05,2024,Q1,February,6,North,Wisconsin,Milwaukee,Clothing,Accessories,Wool Scarf,29.99,15,8.99,0.10,8.50,Consumer,John Smith,26,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7031,2024-02-06,2024,Q1,February,6,South,Texas,Houston,Electronics,Audio,Gaming Headset,139.99,4,41.99,0.05,12.00,Corporate,Sarah Lee,34,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7032,2024-02-06,2024,Q1,February,6,East,New York,Rochester,Furniture,Storage,Night Stand,89.99,5,26.99,0.10,15.00,Home Office,Michael Brown,44,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7033,2024-02-07,2024,Q1,February,6,West,California,San Jose,Clothing,Mens,Athletic Shoes,119.99,4,35.99,0.15,10.00,Consumer,Emily Davis,29,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7034,2024-02-07,2024,Q1,February,6,North,Missouri,St Louis,Electronics,Wearables,Smart Watch,249.99,3,74.99,0.05,12.00,Consumer,John Smith,38,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7035,2024-02-08,2024,Q1,February,6,South,Florida,Tampa,Electronics,Audio,Bluetooth Speaker,99.99,6,29.99,0.10,10.00,Corporate,Sarah Lee,32,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7036,2024-02-08,2024,Q1,February,6,East,Pennsylvania,Pittsburgh,Clothing,Womens,Cashmere Sweater,129.99,5,38.99,0.00,12.00,Consumer,Michael Brown,41,2,3,TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7037,2024-02-09,2024,Q1,February,6,West,Oregon,Eugene,Furniture,Storage,Bookshelf,159.99,3,47.99,0.05,18.00,Home Office,Emily Davis,46,3,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7038,2024-02-09,2024,Q1,February,6,North,Iowa,Des Moines,Electronics,Networking,Mesh Router,119.99,4,35.99,0.10,10.00,Consumer,John Smith,28,2,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7039,2024-02-10,2024,Q1,February,6,South,Texas,San Antonio,Clothing,Mens,Golf Polo,49.99,12,14.99,0.15,8.50,Consumer,Sarah Lee,23,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7040,2024-02-10,2024,Q1,February,6,West,Washington,Spokane,Electronics,Components,Graphics Card,549.99,2,164.99,0.20,18.00,Corporate,Emily Davis,43,3,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7041,2024-03-01,2024,Q1,March,9,North,Illinois,Chicago,Electronics,Computers,Desktop PC,1299.99,2,389.99,0.05,25.00,Corporate,John Smith,50,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7042,2024-03-01,2024,Q1,March,9,South,Texas,Austin,Clothing,Womens,Yoga Pants,54.99,8,16.49,0.00,8.50,Consumer,Sarah Lee,27,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7043,2024-03-02,2024,Q1,March,9,East,New York,New York,Furniture,Tables,Coffee Table,279.99,2,83.99,0.10,22.00,Corporate,Michael Brown,55,3,4,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7044,2024-03-02,2024,Q1,March,9,West,California,Los Angeles,Electronics,Smart Home,Smart Speaker,99.99,5,29.99,0.00,10.00,Home Office,Emily Davis,31,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7045,2024-03-03,2024,Q1,March,9,North,Michigan,Detroit,Clothing,Accessories,Baseball Cap,24.99,12,7.49,0.05,8.50,Consumer,John Smith,19,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7046,2024-03-03,2024,Q1,March,9,South,Florida,Miami,Electronics,Drones,Quadcopter,399.99,2,119.99,0.10,18.00,Corporate,Sarah Lee,38,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7047,2024-03-04,2024,Q1,March,9,East,Pennsylvania,Philadelphia,Furniture,Decor,Wall Mirror,79.99,4,23.99,0.00,12.00,Consumer,Michael Brown,42,1,2,TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7048,2024-03-04,2024,Q1,March,9,West,Oregon,Portland,Clothing,Mens,Flannel Shirt,54.99,6,16.49,0.10,10.00,Home Office,Emily Davis,35,2,3,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7049,2024-03-05,2024,Q1,March,10,North,Ohio,Columbus,Electronics,Streaming,Streaming Stick,39.99,8,11.99,0.05,8.50,Consumer,John Smith,24,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-7050,2024-03-05,2024,Q1,March,10,South,Georgia,Atlanta,Clothing,Womens,Leggings,34.99,10,10.49,0.00,8.50,Consumer,Sarah Lee,22,1,2,FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3051,2024-02-11,West,California,Los Angeles,Electronics,Monitors,Ultrawide Monitor,549.99,2,549.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3052,2024-02-11,North,Illinois,Chicago,Clothing,Mens,Denim Jacket,89.99,5,224.98,0.10,12.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3053,2024-02-12,South,Texas,Houston,Furniture,Chairs,Gaming Chair,299.99,2,299.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3054,2024-02-12,East,New York,Buffalo,Electronics,Audio,Portable Speaker,79.99,4,159.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3055,2024-02-13,West,Washington,Seattle,Clothing,Womens,Rain Jacket,129.99,3,194.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3056,2024-02-13,North,Minnesota,Minneapolis,Electronics,Storage,Portable SSD,89.99,5,224.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3057,2024-02-14,South,Florida,Orlando,Electronics,Phones,Smartphone Case,29.99,15,224.85,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3058,2024-02-14,East,Massachusetts,Boston,Furniture,Lighting,Desk Lamp,59.99,6,179.97,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3059,2024-02-15,West,California,San Diego,Clothing,Accessories,Leather Belt,39.99,8,159.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3060,2024-02-15,North,Ohio,Columbus,Electronics,Accessories,Phone Stand,19.99,12,119.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Profit Margin %' using the formula: (Profit / Sales) * 100. What is the average profit margin for the Electronics category?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Revenue per Unit' using: Sales / Quantity. What is the average revenue per unit for Clothing products?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Total Cost' using: Sales - Profit. What is the total cost for Furniture category?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Discount Amount' using: Sales * Discount. What is the total discount amount given for High Discount orders (Discount &gt; 0.10)?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Net Profit After Shipping' using: Profit - Shipping_Cost. What is the net profit after shipping for the West region?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Sales Performance' that categorizes sales as: 'High' (&gt;1000), 'Medium' (500-1000), 'Low' (&lt;500). How many orders are in the 'High' category?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Discount Impact' that shows: If Discount &gt; 0.10 then 'High Discount', else 'Low Discount'. What is the total sales for High Discount orders?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Customer Age Group' that categorizes: 'Young' (&lt;30), 'Middle' (30-50), 'Senior' (&gt;50). How many customers are in the Senior category?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Order Size' that shows: If Quantity &gt; 5 then 'Bulk Order', else 'Regular Order'. What percentage of orders are Bulk Orders?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Profitability Status' that shows: If Profit &gt; 100 then 'Highly Profitable', if Profit &gt; 0 then 'Profitable', else 'Loss'. How many orders are in Loss?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Customer Value Score' that multiplies Sales by Customer Age and divides by Quantity. What is the average Customer Value Score for Corporate customers?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Shipping Efficiency' that calculates: (Delivery_Days / Order_Processing_Days) + 1. What is the average shipping efficiency?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Full Address' that concatenates City, State, and Region with commas. What is the full address for the order in San Francisco?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Product Code' that extracts the first 3 characters of Product_Name. What is the product code for 'MacBook Pro'?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Order Type' that combines Month and Year. What is the Order Type for orders in February 2024?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Days to Deliver' that calculates the difference between Delivery_Days and Order_Processing_Days. What is the average days to deliver?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Return Status' that shows: If Return_Flag = TRUE then 'Returned', else 'Not Returned'. How many orders were returned?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Discount Level' using a CASE statement: CASE Discount WHEN 0.00 THEN 'No Discount' WHEN 0.05 THEN 'Low Discount' WHEN 0.10 THEN 'Medium Discount' WHEN 0.15 THEN 'High Discount' ELSE 'Very High Discount' END. How many orders have 'Medium Discount'?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Profit Ratio Category' using the formula: IIF(Profit &gt; 100, 'High Profit', IIF(Profit &gt; 0, 'Low Profit', 'Loss')). What is the count of 'High Profit' orders?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Create Calculated Fields</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Calculated Field named 'Total Order Value' that includes Sales plus Shipping_Cost. Then create another calculated field 'Value Category' that categorizes based on Total Order Value. What is the average Total Order Value for 'Premium' orders (&gt;$1000)?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>